--- a/Hoadon/HDRa/12/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/12/HDDienTuMayTinhTien.xlsx
@@ -302,6 +302,1273 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>75/15 trần xuân độ</t>
+        </is>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="13" t="n">
+        <v>5279213.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>469608.0</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>5748821.0</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>2995</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>374 trần phú,phường vũng tàu,tp hồ chí minh</t>
+        </is>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="13" t="n">
+        <v>5636462.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>519775.0</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>6156237.0</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>2996</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>177 tôn đức thắng, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="13" t="n">
+        <v>8352222.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>731814.0</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>9084036.0</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>2997</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="13" t="n">
+        <v>6929240.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>671016.0</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>7600256.0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>63 ngư phủ, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13" t="n">
+        <v>1.0398393E7</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>835308.0</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>1.1233701E7</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Hẻm 540 trần phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13" t="n">
+        <v>5070436.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>481271.0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>5551707.0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>562/30 trần phú, Phường Vũng Tàu , Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="13" t="n">
+        <v>5144445.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>490574.0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>5635019.0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>1507/2 A Đường 30/4 Phường Phước Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="13" t="n">
+        <v>-6917082.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>-553366.0</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>-7470448.0</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13" t="n">
+        <v>6618757.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>615672.0</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>7234429.0</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H16" s="7"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>596 trần phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="13" t="n">
+        <v>1.1486908E7</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>1047134.0</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>1.2534042E7</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="13" t="n">
+        <v>7761881.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>703514.0</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>8465395.0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>337 trần phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="13" t="n">
+        <v>1.2451393E7</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>1169748.0</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>1.3621141E7</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>26/1 trần xuân độ</t>
+        </is>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="13" t="n">
+        <v>5483240.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>508284.0</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>5991524.0</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>3007</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>60A Bạch Đằng</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>60A Bạch Đằng, Phường Vũng Tàu , Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13" t="n">
+        <v>4180026.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>386039.0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>4566065.0</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ không lấy hoá đơn</t>
+        </is>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>3009</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>cảng ka mad</t>
+        </is>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="13" t="n">
+        <v>6849936.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>571084.0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>7421020.0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>3010</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>95 lê lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13" t="n">
+        <v>9441594.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>902529.0</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>1.0344123E7</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>3011</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H24" s="7"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>số 1 phạm hồng thái</t>
+        </is>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13" t="n">
+        <v>5222153.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>499864.0</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>5722017.0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>3012</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Anh đen</t>
+        </is>
+      </c>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13" t="n">
+        <v>4715010.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>416019.0</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>5131029.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HDRa/12/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/12/HDDienTuMayTinhTien.xlsx
@@ -308,17 +308,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -328,33 +328,37 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>75/15 trần xuân độ</t>
-        </is>
-      </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="13" t="n">
-        <v>5279213.0</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>469608.0</v>
-      </c>
+          <t>Hồ Thị Linh Nhi</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Ấp Hoà Nghĩa, Trung Thành Tây, Vũng Liêm, Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>086308005785</t>
+        </is>
+      </c>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>5748821.0</v>
+        <v>9854000.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -373,17 +377,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -393,33 +397,37 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>374 trần phú,phường vũng tàu,tp hồ chí minh</t>
-        </is>
-      </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="13" t="n">
-        <v>5636462.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>519775.0</v>
-      </c>
+          <t>Trần Thị Ngọc Ánh</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>111/46 đường 16, Hiệp Bình Chánh, TP. Thủ Đức, HCM</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>001302006865</t>
+        </is>
+      </c>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>6156237.0</v>
+        <v>8544000.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -438,17 +446,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -458,37 +466,29 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>177 tôn đức thắng, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
+          <t>Nguyễn Nhật Minh</t>
+        </is>
+      </c>
+      <c r="J9" s="6"/>
       <c r="K9" s="6"/>
-      <c r="L9" s="13" t="n">
-        <v>8352222.0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>731814.0</v>
-      </c>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
       <c r="N9" s="13" t="n">
-        <v>0.0</v>
+        <v>230000.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>9084036.0</v>
+        <v>4670000.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -507,17 +507,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -527,33 +527,29 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Khách lẻ</t>
+          <t>Phan Hoàng Nam</t>
         </is>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
-      <c r="L10" s="13" t="n">
-        <v>6929240.0</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>671016.0</v>
-      </c>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>7600256.0</v>
+        <v>1890000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -572,17 +568,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -592,37 +588,29 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>63 ngư phủ, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
+          <t>Phan Hoàng Nam</t>
+        </is>
+      </c>
+      <c r="J11" s="6"/>
       <c r="K11" s="6"/>
-      <c r="L11" s="13" t="n">
-        <v>1.0398393E7</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>835308.0</v>
-      </c>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1.1233701E7</v>
+        <v>200000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -641,17 +629,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -661,37 +649,33 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>Trịnh Đình Toàn</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Hẻm 540 trần phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+          <t>1334/50/3, đường 30/4 phường Phước Thắng, thành phố HCM</t>
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13" t="n">
-        <v>5070436.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>481271.0</v>
-      </c>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
       <c r="N12" s="13" t="n">
-        <v>0.0</v>
+        <v>250000.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>5551707.0</v>
+        <v>4740000.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -710,17 +694,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -730,37 +714,29 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>562/30 trần phú, Phường Vũng Tàu , Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
+          <t>Trịnh Đình Toàn</t>
+        </is>
+      </c>
+      <c r="J13" s="6"/>
       <c r="K13" s="6"/>
-      <c r="L13" s="13" t="n">
-        <v>5144445.0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>490574.0</v>
-      </c>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>5635019.0</v>
+        <v>200000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -779,17 +755,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -799,37 +775,33 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H14" s="7"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>1507/2 A Đường 30/4 Phường Phước Thắng Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Diễm My</t>
+        </is>
+      </c>
+      <c r="J14" s="6"/>
       <c r="K14" s="6"/>
-      <c r="L14" s="13" t="n">
-        <v>-6917082.0</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>-553366.0</v>
-      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
       <c r="N14" s="13" t="n">
-        <v>0.0</v>
+        <v>230000.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>-7470448.0</v>
+        <v>4670000.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn điều chỉnh</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
@@ -844,17 +816,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -864,33 +836,29 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Khách lẻ</t>
+          <t>Trần Gia Hy</t>
         </is>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
-      <c r="L15" s="13" t="n">
-        <v>6618757.0</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>615672.0</v>
-      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
       <c r="N15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>7234429.0</v>
+        <v>4900000.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -909,17 +877,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -929,37 +897,33 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>Thái Minh Nhật</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>596 trần phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+          <t>9A Nguyễn Đức Thuỷ, Rạch Dừa, TP. HCM</t>
         </is>
       </c>
       <c r="K16" s="6"/>
-      <c r="L16" s="13" t="n">
-        <v>1.1486908E7</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>1047134.0</v>
-      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
       <c r="N16" s="13" t="n">
-        <v>0.0</v>
+        <v>522000.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>1.2534042E7</v>
+        <v>3815000.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -978,17 +942,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -998,33 +962,33 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Khách lẻ</t>
-        </is>
-      </c>
-      <c r="J17" s="6"/>
+          <t>Thái Minh Nhiên</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>9A Nguyễn Đức Thuỷ, Rạch Dừa, TP. HCM</t>
+        </is>
+      </c>
       <c r="K17" s="6"/>
-      <c r="L17" s="13" t="n">
-        <v>7761881.0</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>703514.0</v>
-      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
       <c r="N17" s="13" t="n">
-        <v>0.0</v>
+        <v>522000.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>8465395.0</v>
+        <v>3815000.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1043,17 +1007,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -1063,37 +1027,29 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>337 trần phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
+          <t>Nguyễn Trần Nhật Linh</t>
+        </is>
+      </c>
+      <c r="J18" s="6"/>
       <c r="K18" s="6"/>
-      <c r="L18" s="13" t="n">
-        <v>1.2451393E7</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>1169748.0</v>
-      </c>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
       <c r="N18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>1.3621141E7</v>
+        <v>4725000.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1112,17 +1068,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1132,33 +1088,29 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H19" s="7"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>26/1 trần xuân độ</t>
-        </is>
-      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Trần Nhật Linh</t>
+        </is>
+      </c>
+      <c r="J19" s="6"/>
       <c r="K19" s="6"/>
-      <c r="L19" s="13" t="n">
-        <v>5483240.0</v>
-      </c>
-      <c r="M19" s="13" t="n">
-        <v>508284.0</v>
-      </c>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
       <c r="N19" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>5991524.0</v>
+        <v>200000.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1177,17 +1129,17 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1197,37 +1149,29 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>60A Bạch Đằng</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>60A Bạch Đằng, Phường Vũng Tàu , Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
+          <t>Lê Phương Vy</t>
+        </is>
+      </c>
+      <c r="J20" s="6"/>
       <c r="K20" s="6"/>
-      <c r="L20" s="13" t="n">
-        <v>4180026.0</v>
-      </c>
-      <c r="M20" s="13" t="n">
-        <v>386039.0</v>
-      </c>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
       <c r="N20" s="13" t="n">
-        <v>0.0</v>
+        <v>1134000.0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>4566065.0</v>
+        <v>4736000.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -1246,17 +1190,17 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1266,37 +1210,33 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H21" s="7"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Khách lẻ không lấy hoá đơn</t>
-        </is>
-      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Tường Vy</t>
+        </is>
+      </c>
+      <c r="J21" s="6"/>
       <c r="K21" s="6"/>
-      <c r="L21" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M21" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
       <c r="N21" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.0</v>
+        <v>4925000.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn điều chỉnh</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
@@ -1311,53 +1251,49 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H22" s="7"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>cảng ka mad</t>
-        </is>
-      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Ngọc Hân</t>
+        </is>
+      </c>
+      <c r="J22" s="6"/>
       <c r="K22" s="6"/>
-      <c r="L22" s="13" t="n">
-        <v>6849936.0</v>
-      </c>
-      <c r="M22" s="13" t="n">
-        <v>571084.0</v>
-      </c>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
       <c r="N22" s="13" t="n">
-        <v>0.0</v>
+        <v>305000.0</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>7421020.0</v>
+        <v>6095000.0</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -1376,57 +1312,53 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>Đinh Thị Huyền Trang</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>95 lê lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+          <t>Thôn Tân Minh, Xã Môn Sơn, huyện Yên Bình, tỉnh Yên Bái</t>
         </is>
       </c>
       <c r="K23" s="6"/>
-      <c r="L23" s="13" t="n">
-        <v>9441594.0</v>
-      </c>
-      <c r="M23" s="13" t="n">
-        <v>902529.0</v>
-      </c>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
       <c r="N23" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>1.0344123E7</v>
+        <v>4190000.0</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1445,53 +1377,49 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H24" s="7"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>số 1 phạm hồng thái</t>
-        </is>
-      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Mai Vy</t>
+        </is>
+      </c>
+      <c r="J24" s="6"/>
       <c r="K24" s="6"/>
-      <c r="L24" s="13" t="n">
-        <v>5222153.0</v>
-      </c>
-      <c r="M24" s="13" t="n">
-        <v>499864.0</v>
-      </c>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
       <c r="N24" s="13" t="n">
-        <v>0.0</v>
+        <v>230000.0</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>5722017.0</v>
+        <v>4670000.0</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -1510,60 +1438,7368 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Anh đen</t>
+          <t>Hồ Quỳnh Hương</t>
         </is>
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
-      <c r="L25" s="13" t="n">
-        <v>4715010.0</v>
-      </c>
-      <c r="M25" s="13" t="n">
-        <v>416019.0</v>
-      </c>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
       <c r="N25" s="13" t="n">
+        <v>305000.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>6095000.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>3124</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Vũ Thị Thiên Ân</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>730 đường 30/4, P. Phước Thắng, TP. HCM</t>
+        </is>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13" t="n">
+        <v>486000.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>3851000.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Huỳnh Ngô Thiên Phúc</t>
+        </is>
+      </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13" t="n">
+        <v>305000.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>6095000.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>3126</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H28" s="7"/>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Cẩm Ly</t>
+        </is>
+      </c>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13" t="n">
+        <v>1395000.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>8255000.0</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>3127</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Lê Tường Vân</t>
+        </is>
+      </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13" t="n">
+        <v>716000.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>2864000.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>3128</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Phan Thị Yến Nhi</t>
+        </is>
+      </c>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13" t="n">
+        <v>716000.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>2864000.0</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Kiều Tất Toàn</t>
+        </is>
+      </c>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="O25" s="13" t="n">
-        <v>5131029.0</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="O31" s="13" t="n">
+        <v>4990000.0</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H32" s="7"/>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Nguyễn Tường Nguyên</t>
+        </is>
+      </c>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>6100000.0</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H33" s="7"/>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Yến Khoa</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>216/30 Tầm Vu, phường Tân An, quận Ninh Kiều, TP.Cần Thơ</t>
+        </is>
+      </c>
+      <c r="K33" s="6"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13" t="n">
+        <v>250000.0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>4740000.0</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>3132</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H34" s="7"/>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Yến Khoa</t>
+        </is>
+      </c>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>3133</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H35" s="7"/>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Cao Bảo Khanh</t>
+        </is>
+      </c>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>384000.0</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H36" s="7"/>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Diệu Thuỳ</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Số 4- Nguyễn Du- Khu phố 8 Quang Trung- phường Uông Bí- tỉnh Quảng Ninh</t>
+        </is>
+      </c>
+      <c r="K36" s="6"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13" t="n">
+        <v>199000.0</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>3781000.0</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>3135</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H37" s="7"/>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Lê Thị Tố Uyên</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>thôn Quảng Hội 1, Xã Vạn Thắng, tỉnh Khánh Hoà</t>
+        </is>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>3980000.0</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>3136</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H38" s="7"/>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Lê Khánh Linh</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>Bát Tràng-Hà Nội</t>
+        </is>
+      </c>
+      <c r="K38" s="6"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13" t="n">
+        <v>199000.0</v>
+      </c>
+      <c r="O38" s="13" t="n">
+        <v>3781000.0</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>3137</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H39" s="7"/>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Lê Khánh Linh</t>
+        </is>
+      </c>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O39" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H40" s="7"/>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Trần Bảo Ngọc Minh Châu</t>
+        </is>
+      </c>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O40" s="13" t="n">
+        <v>4190000.0</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>3139</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H41" s="7"/>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Võ Lê Hải Phú</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Số 50 đường 23/4 ạ Khu phố 3, phường Phước Hội, Lâm Đồng </t>
+        </is>
+      </c>
+      <c r="K41" s="6"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13" t="n">
+        <v>199000.0</v>
+      </c>
+      <c r="O41" s="13" t="n">
+        <v>3781000.0</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H42" s="7"/>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Trần Minh Anh</t>
+        </is>
+      </c>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="13"/>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O42" s="13" t="n">
+        <v>4990000.0</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>3141</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H43" s="7"/>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Thuý Duyên</t>
+        </is>
+      </c>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13" t="n">
+        <v>305000.0</v>
+      </c>
+      <c r="O43" s="13" t="n">
+        <v>6095000.0</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>3142</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H44" s="7"/>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Tài Minh Đức</t>
+        </is>
+      </c>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13" t="n">
+        <v>293000.0</v>
+      </c>
+      <c r="O44" s="13" t="n">
+        <v>3998000.0</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>3143</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H45" s="7"/>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Phùng Thảo Nhi</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>534B Nguyễn Trung Trực, phường Rạch Giá, An Giang.</t>
+        </is>
+      </c>
+      <c r="K45" s="6"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>3980000.0</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H46" s="7"/>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>Phùng Thảo Nhi</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>534B Nguyễn Trung Trực, phường Rạch Giá, An Giang.</t>
+        </is>
+      </c>
+      <c r="K46" s="6"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O46" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>3145</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H47" s="7"/>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Diệu Linh</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>Thôn Ngọc Giang, Vĩnh Thanh, Đông Anh, Hà Nội</t>
+        </is>
+      </c>
+      <c r="K47" s="6"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13" t="n">
+        <v>250000.0</v>
+      </c>
+      <c r="O47" s="13" t="n">
+        <v>4740000.0</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>3146</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H48" s="7"/>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Diệu Linh</t>
+        </is>
+      </c>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O48" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>3147</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H49" s="7"/>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Thị Mỹ Thiện</t>
+        </is>
+      </c>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13" t="n">
+        <v>230000.0</v>
+      </c>
+      <c r="O49" s="13" t="n">
+        <v>4670000.0</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H50" s="7"/>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>Lê Bảo Hân</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>475 Bùi Minh Trực Phường Bình Đông, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K50" s="6"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13" t="n">
+        <v>199000.0</v>
+      </c>
+      <c r="O50" s="13" t="n">
+        <v>3781000.0</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>3149</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H51" s="7"/>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>Lê Bảo Hân</t>
+        </is>
+      </c>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O51" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H52" s="7"/>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Bảo Uyên</t>
+        </is>
+      </c>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O52" s="13" t="n">
+        <v>4900000.0</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>3151</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H53" s="7"/>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Như Huyền</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>Tổ dân phố 11,phường Đông Hải, Khánh Hòa</t>
+        </is>
+      </c>
+      <c r="K53" s="6"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>4990000.0</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>3152</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H54" s="7"/>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Như Huyền</t>
+        </is>
+      </c>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O54" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>3153</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H55" s="7"/>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>Lê Thị Mỹ Duyên</t>
+        </is>
+      </c>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13" t="n">
+        <v>305000.0</v>
+      </c>
+      <c r="O55" s="13" t="n">
+        <v>6095000.0</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H56" s="7"/>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>Hà Huỳnh Nhựt Nguyên</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>Số nhà 130, Khóm 1, TT Lai Vung, Lai Vung, Đồng Tháp</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>087204008371</t>
+        </is>
+      </c>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O56" s="13" t="n">
+        <v>1.0534E7</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>3155</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H57" s="7"/>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Huỳnh Minh Trí</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>2/20 Lương Văn Can, P. Vũng Tàu, TP. HCM</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>077208011605</t>
+        </is>
+      </c>
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
+      <c r="N57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O57" s="13" t="n">
+        <v>9564000.0</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>3156</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H58" s="7"/>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Mạnh Hùng</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>54/15/2 Trần Bích San, P. Trần Quang Khải, TP. Nam Định</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>036203004948</t>
+        </is>
+      </c>
+      <c r="L58" s="13"/>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O58" s="13" t="n">
+        <v>1.1064E7</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>3157</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H59" s="7"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>Bùi Thị Minh Ngọc</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>Khóm 1, TT Vũng Liêm, Vũng Liêm, Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>086308006784</t>
+        </is>
+      </c>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>1.0534E7</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>3158</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H60" s="7"/>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Lan Anh</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>P408-C3, Thanh Xuân Bắc, Thanh Xuân, Hà Nội</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>001302035762</t>
+        </is>
+      </c>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O60" s="13" t="n">
+        <v>1.0534E7</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>3159</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>Điền Thanh Thiên</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>569/16 Nguyễn An Ninh, P. Vũng Tàu, TP. HCM</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>077208011631</t>
+        </is>
+      </c>
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>1.0534E7</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>3160</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H62" s="7"/>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>Huỳnh Hồng Hân</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>Ấp 7, xã Đại Hải, thành phố Cần Thơ</t>
+        </is>
+      </c>
+      <c r="K62" s="6"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>4190000.0</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>3161</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H63" s="7"/>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>Tạ Kiều Anh</t>
+        </is>
+      </c>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>9000000.0</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>3162</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H64" s="7"/>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Lê Thiên Bảo</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Lê Thiên Bảo</t>
+        </is>
+      </c>
+      <c r="K64" s="6"/>
+      <c r="L64" s="13"/>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>7974000.0</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H65" s="7"/>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>Lê Dương Thiên Lam</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>PA1616, chung cư DIC Phoenic, phường Tam Thắng, TP HCM</t>
+        </is>
+      </c>
+      <c r="K65" s="6"/>
+      <c r="L65" s="13"/>
+      <c r="M65" s="13"/>
+      <c r="N65" s="13" t="n">
+        <v>3169406.0</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>4750594.0</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>3164</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H66" s="7"/>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Hoàng Hiệp Anh</t>
+        </is>
+      </c>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13" t="n">
+        <v>461000.0</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>3499000.0</v>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>3165</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H67" s="7"/>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>Phan Ngọc Minh</t>
+        </is>
+      </c>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
+      <c r="N67" s="13" t="n">
+        <v>230000.0</v>
+      </c>
+      <c r="O67" s="13" t="n">
+        <v>4670000.0</v>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>3166</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H68" s="7"/>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>Dương Thị Kim Ngân</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>Cẩm lý- Lục Nam- Bắc Ninh</t>
+        </is>
+      </c>
+      <c r="K68" s="6"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13" t="n">
+        <v>199000.0</v>
+      </c>
+      <c r="O68" s="13" t="n">
+        <v>3781000.0</v>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H69" s="7"/>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>Dương Thị Kim Ngân</t>
+        </is>
+      </c>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O69" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>3168</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H70" s="7"/>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>Bùi Thị Tố Như</t>
+        </is>
+      </c>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O70" s="13" t="n">
+        <v>4900000.0</v>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>3169</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H71" s="7"/>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Tiến Quân Bảo</t>
+        </is>
+      </c>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="13"/>
+      <c r="M71" s="13"/>
+      <c r="N71" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O71" s="13" t="n">
+        <v>3980000.0</v>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>3170</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H72" s="7"/>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thị Kim Tuyết</t>
+        </is>
+      </c>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="13"/>
+      <c r="M72" s="13"/>
+      <c r="N72" s="13" t="n">
+        <v>305000.0</v>
+      </c>
+      <c r="O72" s="13" t="n">
+        <v>6095000.0</v>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H73" s="7"/>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thị Thu Hồng</t>
+        </is>
+      </c>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="13"/>
+      <c r="M73" s="13"/>
+      <c r="N73" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O73" s="13" t="n">
+        <v>4900000.0</v>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>68.0</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>3172</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H74" s="7"/>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Duy Khánh</t>
+        </is>
+      </c>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="13"/>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13" t="n">
+        <v>293000.0</v>
+      </c>
+      <c r="O74" s="13" t="n">
+        <v>4051000.0</v>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>3173</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H75" s="7"/>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Duy Mạnh</t>
+        </is>
+      </c>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="13"/>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13" t="n">
+        <v>293000.0</v>
+      </c>
+      <c r="O75" s="13" t="n">
+        <v>3667000.0</v>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H76" s="7"/>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Minh Thư</t>
+        </is>
+      </c>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="13"/>
+      <c r="M76" s="13"/>
+      <c r="N76" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O76" s="13" t="n">
+        <v>4925000.0</v>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>3175</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H77" s="7"/>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Minh Tâm</t>
+        </is>
+      </c>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="13"/>
+      <c r="M77" s="13"/>
+      <c r="N77" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O77" s="13" t="n">
+        <v>3980000.0</v>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>72.0</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>3176</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H78" s="7"/>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Đinh Thị Thuý</t>
+        </is>
+      </c>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="13"/>
+      <c r="M78" s="13"/>
+      <c r="N78" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O78" s="13" t="n">
+        <v>1.3275E7</v>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>73.0</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>3177</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H79" s="7"/>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>Võ Anh Kiệt</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>Khu vực 15, Châu Văn Liêm, Ô Môn, Cần Thơ</t>
+        </is>
+      </c>
+      <c r="K79" s="6"/>
+      <c r="L79" s="13"/>
+      <c r="M79" s="13"/>
+      <c r="N79" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O79" s="13" t="n">
+        <v>4190000.0</v>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>3178</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H80" s="7"/>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thắng</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>52/33 Đường số 4, Hiệp Bình Phước, Thủ Đức</t>
+        </is>
+      </c>
+      <c r="K80" s="6"/>
+      <c r="L80" s="13"/>
+      <c r="M80" s="13"/>
+      <c r="N80" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="O80" s="13" t="n">
+        <v>3780000.0</v>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>3179</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H81" s="7"/>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Tuấn Bình Phước</t>
+        </is>
+      </c>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="13"/>
+      <c r="M81" s="13"/>
+      <c r="N81" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O81" s="13" t="n">
+        <v>5870000.0</v>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>3180</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H82" s="7"/>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>Đặng Tiến Dũng</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>27A Lý Tự Trọng, P. Yên Bái, Lào Cai</t>
+        </is>
+      </c>
+      <c r="K82" s="6"/>
+      <c r="L82" s="13"/>
+      <c r="M82" s="13"/>
+      <c r="N82" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O82" s="13" t="n">
+        <v>4190000.0</v>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>77.0</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H83" s="7"/>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>Đặng Tiến Dũng</t>
+        </is>
+      </c>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="13"/>
+      <c r="M83" s="13"/>
+      <c r="N83" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O83" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>78.0</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H84" s="7"/>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>Khương Lê Bảo Lâm</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>53 Trần Tế Xương, Cam Lâm, Khánh Hoà</t>
+        </is>
+      </c>
+      <c r="K84" s="6"/>
+      <c r="L84" s="13"/>
+      <c r="M84" s="13"/>
+      <c r="N84" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O84" s="13" t="n">
+        <v>1.26E7</v>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>3183</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H85" s="7"/>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>Lâm Phát Thịnh</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>2/39, Lý Bôn, phường 4, TP Cà Mau</t>
+        </is>
+      </c>
+      <c r="K85" s="6"/>
+      <c r="L85" s="13"/>
+      <c r="M85" s="13"/>
+      <c r="N85" s="13" t="n">
+        <v>250000.0</v>
+      </c>
+      <c r="O85" s="13" t="n">
+        <v>4740000.0</v>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>3184</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H86" s="7"/>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>Phan Tấn Đạt</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>Xã Mỹ Thuận, huyện Bình Tân, Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="K86" s="6"/>
+      <c r="L86" s="13"/>
+      <c r="M86" s="13"/>
+      <c r="N86" s="13" t="n">
+        <v>250000.0</v>
+      </c>
+      <c r="O86" s="13" t="n">
+        <v>4740000.0</v>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>81.0</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>3185</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H87" s="7"/>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Anh</t>
+        </is>
+      </c>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="13"/>
+      <c r="M87" s="13"/>
+      <c r="N87" s="13" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="O87" s="13" t="n">
+        <v>1.114E7</v>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>3186</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H88" s="7"/>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Khen</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>Khu phố Tân Phú - Tân Hiệp - Tp. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K88" s="6"/>
+      <c r="L88" s="13"/>
+      <c r="M88" s="13"/>
+      <c r="N88" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O88" s="13" t="n">
+        <v>3980000.0</v>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>83.0</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>3187</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H89" s="7"/>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Phúc Anh Hào</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>105 đường A4 Phường Tân Bình Quận Tân Bình TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K89" s="6"/>
+      <c r="L89" s="13"/>
+      <c r="M89" s="13"/>
+      <c r="N89" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O89" s="13" t="n">
+        <v>4900000.0</v>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>84.0</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H90" s="7"/>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Thuỳ Dương</t>
+        </is>
+      </c>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="13"/>
+      <c r="M90" s="13"/>
+      <c r="N90" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="O90" s="13" t="n">
+        <v>1.296E7</v>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>85.0</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H91" s="7"/>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>Võ Lê Minh Hồng</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>57/25 đường số 7, Hiệp Bình Phước, Thủ Đức, TP. HCM</t>
+        </is>
+      </c>
+      <c r="K91" s="6"/>
+      <c r="L91" s="13"/>
+      <c r="M91" s="13"/>
+      <c r="N91" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>3980000.0</v>
+      </c>
+      <c r="P91" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>3190</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H92" s="7"/>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>Văn Hồng Diễm</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">435/56, ĐT 743A, khu phố Đông Tân, phường Dĩ An, Tp Hồ Chí Minh </t>
+        </is>
+      </c>
+      <c r="K92" s="6"/>
+      <c r="L92" s="13"/>
+      <c r="M92" s="13"/>
+      <c r="N92" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="O92" s="13" t="n">
+        <v>9680000.0</v>
+      </c>
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q92" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>87.0</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H93" s="7"/>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>Văn Hồng Diễm</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">435/56, ĐT 743A, khu phố Đông Tân, phường Dĩ An, Tp Hồ Chí Minh </t>
+        </is>
+      </c>
+      <c r="K93" s="6"/>
+      <c r="L93" s="13"/>
+      <c r="M93" s="13"/>
+      <c r="N93" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O93" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P93" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q93" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>88.0</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>3192</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H94" s="7"/>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Đức An</t>
+        </is>
+      </c>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="13"/>
+      <c r="M94" s="13"/>
+      <c r="N94" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="O94" s="13" t="n">
+        <v>4191000.0</v>
+      </c>
+      <c r="P94" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q94" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>89.0</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>3193</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H95" s="7"/>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>Trần Minh Khoa</t>
+        </is>
+      </c>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="13"/>
+      <c r="M95" s="13"/>
+      <c r="N95" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O95" s="13" t="n">
+        <v>4900000.0</v>
+      </c>
+      <c r="P95" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q95" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>3194</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H96" s="7"/>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Ngọc Minh Châu</t>
+        </is>
+      </c>
+      <c r="J96" s="6"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="13"/>
+      <c r="M96" s="13"/>
+      <c r="N96" s="13" t="n">
+        <v>341000.0</v>
+      </c>
+      <c r="O96" s="13" t="n">
+        <v>3950000.0</v>
+      </c>
+      <c r="P96" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q96" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>91.0</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>3195</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H97" s="7"/>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Phạm Bảo Thy</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>156/8 Đặng Văn Ngữ P.13 Q.Phú Nhuận, TP. HCM</t>
+        </is>
+      </c>
+      <c r="K97" s="6"/>
+      <c r="L97" s="13"/>
+      <c r="M97" s="13"/>
+      <c r="N97" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O97" s="13" t="n">
+        <v>3980000.0</v>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q97" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>92.0</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>3196</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H98" s="7"/>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>Đoàn Thanh Trúc</t>
+        </is>
+      </c>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="13"/>
+      <c r="M98" s="13"/>
+      <c r="N98" s="13" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="O98" s="13" t="n">
+        <v>1.114E7</v>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q98" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>93.0</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>3197</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H99" s="7"/>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>Hứa Uyên Bình</t>
+        </is>
+      </c>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="13"/>
+      <c r="M99" s="13"/>
+      <c r="N99" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O99" s="13" t="n">
+        <v>5870000.0</v>
+      </c>
+      <c r="P99" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q99" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>94.0</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>3198</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H100" s="7"/>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Đức</t>
+        </is>
+      </c>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="13"/>
+      <c r="M100" s="13"/>
+      <c r="N100" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O100" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="P100" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q100" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>95.0</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>3199</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H101" s="7"/>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>Vương Thị Hào</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>Ngõ 88 Nguyễn chính,  Tân Mai,  Thịnh Liệt,  Hoàng Mai,  Hà Nội</t>
+        </is>
+      </c>
+      <c r="K101" s="6"/>
+      <c r="L101" s="13"/>
+      <c r="M101" s="13"/>
+      <c r="N101" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O101" s="13" t="n">
+        <v>4190000.0</v>
+      </c>
+      <c r="P101" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q101" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>96.0</v>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H102" s="7"/>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Huyền Trang</t>
+        </is>
+      </c>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="13"/>
+      <c r="M102" s="13"/>
+      <c r="N102" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O102" s="13" t="n">
+        <v>4990000.0</v>
+      </c>
+      <c r="P102" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q102" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>97.0</v>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H103" s="7"/>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Tiến Đạt</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>xã Bình An huyện Bình Lục tỉnh Ninh Bình</t>
+        </is>
+      </c>
+      <c r="K103" s="6"/>
+      <c r="L103" s="13"/>
+      <c r="M103" s="13"/>
+      <c r="N103" s="13" t="n">
+        <v>199000.0</v>
+      </c>
+      <c r="O103" s="13" t="n">
+        <v>3781000.0</v>
+      </c>
+      <c r="P103" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q103" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>98.0</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H104" s="7"/>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Thị Kim Loan</t>
+        </is>
+      </c>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="13"/>
+      <c r="M104" s="13"/>
+      <c r="N104" s="13" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="O104" s="13" t="n">
+        <v>1.114E7</v>
+      </c>
+      <c r="P104" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q104" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>3203</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H105" s="7"/>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>Lê Hoài Nam</t>
+        </is>
+      </c>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="13"/>
+      <c r="M105" s="13"/>
+      <c r="N105" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O105" s="13" t="n">
+        <v>4925000.0</v>
+      </c>
+      <c r="P105" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q105" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H106" s="7"/>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Vũ Đăng Khoa</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">519-Hùng Vương-thị trấn Di Linh-tỉnh Lâm Đồng </t>
+        </is>
+      </c>
+      <c r="K106" s="6"/>
+      <c r="L106" s="13"/>
+      <c r="M106" s="13"/>
+      <c r="N106" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O106" s="13" t="n">
+        <v>4990000.0</v>
+      </c>
+      <c r="P106" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q106" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>101.0</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H107" s="7"/>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Yến Như</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>Ấp An Nhơn, Trung Thành, Vũng Liêm, Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>086308005976</t>
+        </is>
+      </c>
+      <c r="L107" s="13"/>
+      <c r="M107" s="13"/>
+      <c r="N107" s="13" t="n">
+        <v>199000.0</v>
+      </c>
+      <c r="O107" s="13" t="n">
+        <v>8445000.0</v>
+      </c>
+      <c r="P107" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q107" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>102.0</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H108" s="7"/>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>Vũ Quang Thu Phương</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>Xóm Yên Xuân, Tân Xuân, Tân Kỳ, Nghệ An</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>040308026028</t>
+        </is>
+      </c>
+      <c r="L108" s="13"/>
+      <c r="M108" s="13"/>
+      <c r="N108" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O108" s="13" t="n">
+        <v>9854000.0</v>
+      </c>
+      <c r="P108" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q108" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>103.0</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>3207</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H109" s="7"/>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>Lương Quang Sơn</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>Phòng B303 chung cư 15 tầng , đường Ngô Đức kế , P. Tam Thắng, TP.HCM</t>
+        </is>
+      </c>
+      <c r="K109" s="6"/>
+      <c r="L109" s="13"/>
+      <c r="M109" s="13"/>
+      <c r="N109" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="O109" s="13" t="n">
+        <v>3860000.0</v>
+      </c>
+      <c r="P109" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q109" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>104.0</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H110" s="7"/>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Ngọc Mai Phương</t>
+        </is>
+      </c>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6"/>
+      <c r="L110" s="13"/>
+      <c r="M110" s="13"/>
+      <c r="N110" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O110" s="13" t="n">
+        <v>4725000.0</v>
+      </c>
+      <c r="P110" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q110" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>105.0</v>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H111" s="7"/>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Ngọc Mai Phương</t>
+        </is>
+      </c>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="13"/>
+      <c r="M111" s="13"/>
+      <c r="N111" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O111" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P111" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q111" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>106.0</v>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>3210</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H112" s="7"/>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Trang Quỳnh Hân</t>
+        </is>
+      </c>
+      <c r="J112" s="6"/>
+      <c r="K112" s="6"/>
+      <c r="L112" s="13"/>
+      <c r="M112" s="13"/>
+      <c r="N112" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O112" s="13" t="n">
+        <v>5870000.0</v>
+      </c>
+      <c r="P112" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q112" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>107.0</v>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H113" s="7"/>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Minh Thư</t>
+        </is>
+      </c>
+      <c r="J113" s="6"/>
+      <c r="K113" s="6"/>
+      <c r="L113" s="13"/>
+      <c r="M113" s="13"/>
+      <c r="N113" s="13" t="n">
+        <v>3060000.0</v>
+      </c>
+      <c r="O113" s="13" t="n">
+        <v>1.664E7</v>
+      </c>
+      <c r="P113" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q113" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>108.0</v>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H114" s="7"/>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Khánh Huyền</t>
+        </is>
+      </c>
+      <c r="J114" s="6"/>
+      <c r="K114" s="6"/>
+      <c r="L114" s="13"/>
+      <c r="M114" s="13"/>
+      <c r="N114" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="O114" s="13" t="n">
+        <v>3780000.0</v>
+      </c>
+      <c r="P114" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q114" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>109.0</v>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="inlineStr">
+        <is>
+          <t>1600699279</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CP DƯỢC PHẨM AGIMEXPHARM</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>Số 27 Nguyễn Thái Học, Phường Long Xuyên, Tỉnh An Giang, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K115" s="6"/>
+      <c r="L115" s="13"/>
+      <c r="M115" s="13"/>
+      <c r="N115" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O115" s="13" t="n">
+        <v>3184000.0</v>
+      </c>
+      <c r="P115" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q115" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>110.0</v>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>3214</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H116" s="7"/>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Thị Khánh Hoà</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>Tổ dân phố Trung, Phường Nam Triệu, Hải Phòng</t>
+        </is>
+      </c>
+      <c r="K116" s="6"/>
+      <c r="L116" s="13"/>
+      <c r="M116" s="13"/>
+      <c r="N116" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O116" s="13" t="n">
+        <v>4990000.0</v>
+      </c>
+      <c r="P116" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q116" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="n">
+        <v>111.0</v>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>3215</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H117" s="7"/>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Quang Vinh</t>
+        </is>
+      </c>
+      <c r="J117" s="6"/>
+      <c r="K117" s="6"/>
+      <c r="L117" s="13"/>
+      <c r="M117" s="13"/>
+      <c r="N117" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O117" s="13" t="n">
+        <v>3580000.0</v>
+      </c>
+      <c r="P117" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q117" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>112.0</v>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>3216</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H118" s="7"/>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Hà</t>
+        </is>
+      </c>
+      <c r="J118" s="6"/>
+      <c r="K118" s="6"/>
+      <c r="L118" s="13"/>
+      <c r="M118" s="13"/>
+      <c r="N118" s="13" t="n">
+        <v>250000.0</v>
+      </c>
+      <c r="O118" s="13" t="n">
+        <v>4740000.0</v>
+      </c>
+      <c r="P118" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q118" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="n">
+        <v>113.0</v>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>3217</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H119" s="7"/>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>Choong Su Linh</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>171/25/1B Nguyễn An Ninh, Tam Thắng, HCM</t>
+        </is>
+      </c>
+      <c r="K119" s="6"/>
+      <c r="L119" s="13"/>
+      <c r="M119" s="13"/>
+      <c r="N119" s="13" t="n">
+        <v>237000.0</v>
+      </c>
+      <c r="O119" s="13" t="n">
+        <v>4938000.0</v>
+      </c>
+      <c r="P119" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q119" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="n">
+        <v>114.0</v>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>3218</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H120" s="7"/>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Trần Minh Thư</t>
+        </is>
+      </c>
+      <c r="J120" s="6"/>
+      <c r="K120" s="6"/>
+      <c r="L120" s="13"/>
+      <c r="M120" s="13"/>
+      <c r="N120" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="O120" s="13" t="n">
+        <v>8950000.0</v>
+      </c>
+      <c r="P120" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q120" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="n">
+        <v>115.0</v>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>3219</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H121" s="7"/>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Trần Minh Thư</t>
+        </is>
+      </c>
+      <c r="J121" s="6"/>
+      <c r="K121" s="6"/>
+      <c r="L121" s="13"/>
+      <c r="M121" s="13"/>
+      <c r="N121" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O121" s="13" t="n">
+        <v>400000.0</v>
+      </c>
+      <c r="P121" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q121" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="n">
+        <v>116.0</v>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H122" s="7"/>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>Cao Vân Vân</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="inlineStr">
+        <is>
+          <t>Khu đô thị Dragon Homes Metropolis, Đường T7 đại lộ Trần Hưng Đạo, Phường Cam Đường (Bắc Cường), Tp Lào Cai, Tỉnh Lào Cai</t>
+        </is>
+      </c>
+      <c r="K122" s="6"/>
+      <c r="L122" s="13"/>
+      <c r="M122" s="13"/>
+      <c r="N122" s="13" t="n">
+        <v>3360000.0</v>
+      </c>
+      <c r="O122" s="13" t="n">
+        <v>6460000.0</v>
+      </c>
+      <c r="P122" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q122" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="n">
+        <v>117.0</v>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>3221</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H123" s="7"/>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Phạm Đăng Khoa</t>
+        </is>
+      </c>
+      <c r="J123" s="6"/>
+      <c r="K123" s="6"/>
+      <c r="L123" s="13"/>
+      <c r="M123" s="13"/>
+      <c r="N123" s="13" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="O123" s="13" t="n">
+        <v>1.074E7</v>
+      </c>
+      <c r="P123" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q123" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>118.0</v>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>3222</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H124" s="7"/>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Phạm Đăng Khoa</t>
+        </is>
+      </c>
+      <c r="J124" s="6"/>
+      <c r="K124" s="6"/>
+      <c r="L124" s="13"/>
+      <c r="M124" s="13"/>
+      <c r="N124" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O124" s="13" t="n">
+        <v>400000.0</v>
+      </c>
+      <c r="P124" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q124" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="n">
+        <v>119.0</v>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>3223</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H125" s="7"/>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>Ngô Phạm Hoàng Nam</t>
+        </is>
+      </c>
+      <c r="J125" s="6"/>
+      <c r="K125" s="6"/>
+      <c r="L125" s="13"/>
+      <c r="M125" s="13"/>
+      <c r="N125" s="13" t="n">
+        <v>784000.0</v>
+      </c>
+      <c r="O125" s="13" t="n">
+        <v>3136000.0</v>
+      </c>
+      <c r="P125" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q125" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H126" s="7"/>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Tấn Đạt</t>
+        </is>
+      </c>
+      <c r="J126" s="6"/>
+      <c r="K126" s="6"/>
+      <c r="L126" s="13"/>
+      <c r="M126" s="13"/>
+      <c r="N126" s="13" t="n">
+        <v>792000.0</v>
+      </c>
+      <c r="O126" s="13" t="n">
+        <v>3168000.0</v>
+      </c>
+      <c r="P126" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q126" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n">
+        <v>121.0</v>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>3225</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H127" s="7"/>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Tấn Đạt</t>
+        </is>
+      </c>
+      <c r="J127" s="6"/>
+      <c r="K127" s="6"/>
+      <c r="L127" s="13"/>
+      <c r="M127" s="13"/>
+      <c r="N127" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O127" s="13" t="n">
+        <v>205000.0</v>
+      </c>
+      <c r="P127" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q127" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>122.0</v>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H128" s="7"/>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>Lê Hoàng Nam</t>
+        </is>
+      </c>
+      <c r="J128" s="6"/>
+      <c r="K128" s="6"/>
+      <c r="L128" s="13"/>
+      <c r="M128" s="13"/>
+      <c r="N128" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O128" s="13" t="n">
+        <v>4925000.0</v>
+      </c>
+      <c r="P128" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q128" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>123.0</v>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H129" s="7"/>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Tấn Đạt</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 11, ấp Quảng Đông, xã Nghĩa Thành, TPHCM</t>
+        </is>
+      </c>
+      <c r="K129" s="6"/>
+      <c r="L129" s="13"/>
+      <c r="M129" s="13"/>
+      <c r="N129" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O129" s="13" t="n">
+        <v>4925000.0</v>
+      </c>
+      <c r="P129" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q129" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>124.0</v>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H130" s="7"/>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>Mai Hoàng Châu</t>
+        </is>
+      </c>
+      <c r="J130" s="6"/>
+      <c r="K130" s="6"/>
+      <c r="L130" s="13"/>
+      <c r="M130" s="13"/>
+      <c r="N130" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O130" s="13" t="n">
+        <v>4725000.0</v>
+      </c>
+      <c r="P130" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q130" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>125.0</v>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>3229</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H131" s="7"/>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>Mai Hoàng Châu</t>
+        </is>
+      </c>
+      <c r="J131" s="6"/>
+      <c r="K131" s="6"/>
+      <c r="L131" s="13"/>
+      <c r="M131" s="13"/>
+      <c r="N131" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O131" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P131" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q131" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>126.0</v>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H132" s="7"/>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Anh</t>
+        </is>
+      </c>
+      <c r="J132" s="6"/>
+      <c r="K132" s="6"/>
+      <c r="L132" s="13"/>
+      <c r="M132" s="13"/>
+      <c r="N132" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O132" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P132" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q132" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>127.0</v>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H133" s="7"/>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Đắc Thái Hưng</t>
+        </is>
+      </c>
+      <c r="J133" s="6"/>
+      <c r="K133" s="6"/>
+      <c r="L133" s="13"/>
+      <c r="M133" s="13"/>
+      <c r="N133" s="13" t="n">
+        <v>1890000.0</v>
+      </c>
+      <c r="O133" s="13" t="n">
+        <v>7560000.0</v>
+      </c>
+      <c r="P133" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q133" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H134" s="7"/>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>Văn Thị Khánh Ly</t>
+        </is>
+      </c>
+      <c r="J134" s="6"/>
+      <c r="K134" s="6"/>
+      <c r="L134" s="13"/>
+      <c r="M134" s="13"/>
+      <c r="N134" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O134" s="13" t="n">
+        <v>6400000.0</v>
+      </c>
+      <c r="P134" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q134" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n">
+        <v>129.0</v>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>3233</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H135" s="7"/>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>Hứa Thị Lý</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>Thôn Khuối Kháo, Xã Nhân Lý, Tỉnh Lạng Sơn</t>
+        </is>
+      </c>
+      <c r="K135" s="6"/>
+      <c r="L135" s="13"/>
+      <c r="M135" s="13"/>
+      <c r="N135" s="13" t="n">
+        <v>838000.0</v>
+      </c>
+      <c r="O135" s="13" t="n">
+        <v>3352000.0</v>
+      </c>
+      <c r="P135" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q135" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H136" s="7"/>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Vũ Quỳnh Nhi</t>
+        </is>
+      </c>
+      <c r="J136" s="6"/>
+      <c r="K136" s="6"/>
+      <c r="L136" s="13"/>
+      <c r="M136" s="13"/>
+      <c r="N136" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O136" s="13" t="n">
+        <v>3980000.0</v>
+      </c>
+      <c r="P136" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q136" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="n">
+        <v>131.0</v>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>3235</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H137" s="7"/>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>Cao Thị Thảo Uyên</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>Thôn Hội Lâm xã Nhân Hoà tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="K137" s="6"/>
+      <c r="L137" s="13"/>
+      <c r="M137" s="13"/>
+      <c r="N137" s="13" t="n">
+        <v>6000000.0</v>
+      </c>
+      <c r="O137" s="13" t="n">
+        <v>2.249E7</v>
+      </c>
+      <c r="P137" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q137" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H138" s="7"/>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>Lưu Quang Tôn</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>32 Phạm Văn Chí, P. Bình Tiền, TP. HCM</t>
+        </is>
+      </c>
+      <c r="K138" s="6"/>
+      <c r="L138" s="13"/>
+      <c r="M138" s="13"/>
+      <c r="N138" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O138" s="13" t="n">
+        <v>1125000.0</v>
+      </c>
+      <c r="P138" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q138" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="n">
+        <v>133.0</v>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>3237</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H139" s="7"/>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Ngọc My</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t>153/15/9 Nguyễn Thượng  Hiền Phường 6 Quận Bình Thạnh Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K139" s="6"/>
+      <c r="L139" s="13"/>
+      <c r="M139" s="13"/>
+      <c r="N139" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O139" s="13" t="n">
+        <v>4190000.0</v>
+      </c>
+      <c r="P139" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q139" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n">
+        <v>134.0</v>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>3238</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H140" s="7"/>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Nguyên</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Thôn 2 xã Đức Liễu huyện Bù Đăng tỉnh Bình Phước</t>
+        </is>
+      </c>
+      <c r="K140" s="6"/>
+      <c r="L140" s="13"/>
+      <c r="M140" s="13"/>
+      <c r="N140" s="13" t="n">
+        <v>199000.0</v>
+      </c>
+      <c r="O140" s="13" t="n">
+        <v>3781000.0</v>
+      </c>
+      <c r="P140" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q140" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="n">
+        <v>135.0</v>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>3239</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H141" s="7"/>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Phan Hồng Lam</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="inlineStr">
+        <is>
+          <t>số 30, ngõ 205/196, đường Xuân Đỉnh, phường Xuân Đỉnh, Hà Nội</t>
+        </is>
+      </c>
+      <c r="K141" s="6"/>
+      <c r="L141" s="13"/>
+      <c r="M141" s="13"/>
+      <c r="N141" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O141" s="13" t="n">
+        <v>4990000.0</v>
+      </c>
+      <c r="P141" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q141" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDRa/12/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/12/HDDienTuMayTinhTien.xlsx
@@ -8805,6 +8805,2075 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>136.0</v>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>3240</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H142" s="7"/>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Ngọc Mai Phương</t>
+        </is>
+      </c>
+      <c r="J142" s="6"/>
+      <c r="K142" s="6"/>
+      <c r="L142" s="13"/>
+      <c r="M142" s="13"/>
+      <c r="N142" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O142" s="13" t="n">
+        <v>4925000.0</v>
+      </c>
+      <c r="P142" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q142" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>137.0</v>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>3241</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H143" s="7"/>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Ngọc Mai Phương</t>
+        </is>
+      </c>
+      <c r="J143" s="6"/>
+      <c r="K143" s="6"/>
+      <c r="L143" s="13"/>
+      <c r="M143" s="13"/>
+      <c r="N143" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O143" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P143" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q143" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>138.0</v>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>3242</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H144" s="7"/>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Thảo Vy</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>302A, Trương Định, phường An Hội, Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="K144" s="6"/>
+      <c r="L144" s="13"/>
+      <c r="M144" s="13"/>
+      <c r="N144" s="13" t="n">
+        <v>305000.0</v>
+      </c>
+      <c r="O144" s="13" t="n">
+        <v>6095000.0</v>
+      </c>
+      <c r="P144" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q144" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n">
+        <v>139.0</v>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>3243</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H145" s="7"/>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>Lê Quang Thiện</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr">
+        <is>
+          <t>51/10 Lương Văn Can, P. Vũng Tàu, TP.HCM</t>
+        </is>
+      </c>
+      <c r="K145" s="6"/>
+      <c r="L145" s="13"/>
+      <c r="M145" s="13"/>
+      <c r="N145" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O145" s="13" t="n">
+        <v>5870000.0</v>
+      </c>
+      <c r="P145" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q145" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>140.0</v>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>3244</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H146" s="7"/>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Hà My</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="inlineStr">
+        <is>
+          <t>133 Tựu Liệt, Tam Hiệp, Thanh Trì, Hà Nội</t>
+        </is>
+      </c>
+      <c r="K146" s="6"/>
+      <c r="L146" s="13"/>
+      <c r="M146" s="13"/>
+      <c r="N146" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="O146" s="13" t="n">
+        <v>1.094E7</v>
+      </c>
+      <c r="P146" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q146" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n">
+        <v>141.0</v>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>3245</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H147" s="7"/>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thuý Vy</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="inlineStr">
+        <is>
+          <t>K2/12 KP Thái Hoà P Long Hưng Biên Hoà Đồng Nai</t>
+        </is>
+      </c>
+      <c r="K147" s="6"/>
+      <c r="L147" s="13"/>
+      <c r="M147" s="13"/>
+      <c r="N147" s="13" t="n">
+        <v>3020000.0</v>
+      </c>
+      <c r="O147" s="13" t="n">
+        <v>6800000.0</v>
+      </c>
+      <c r="P147" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q147" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>142.0</v>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>3246</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H148" s="7"/>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>Đỗ Thi Linh</t>
+        </is>
+      </c>
+      <c r="J148" s="6"/>
+      <c r="K148" s="6"/>
+      <c r="L148" s="13"/>
+      <c r="M148" s="13"/>
+      <c r="N148" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O148" s="13" t="n">
+        <v>3980000.0</v>
+      </c>
+      <c r="P148" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q148" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n">
+        <v>143.0</v>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>3247</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H149" s="7"/>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>Đỗ Thi Linh</t>
+        </is>
+      </c>
+      <c r="J149" s="6"/>
+      <c r="K149" s="6"/>
+      <c r="L149" s="13"/>
+      <c r="M149" s="13"/>
+      <c r="N149" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O149" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P149" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q149" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>144.0</v>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>3248</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H150" s="7"/>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thuỳ Trang</t>
+        </is>
+      </c>
+      <c r="J150" s="6"/>
+      <c r="K150" s="6"/>
+      <c r="L150" s="13"/>
+      <c r="M150" s="13"/>
+      <c r="N150" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="O150" s="13" t="n">
+        <v>1.0295E7</v>
+      </c>
+      <c r="P150" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q150" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="n">
+        <v>145.0</v>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>3249</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H151" s="7"/>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>Lương Nguyễn Hà Phương</t>
+        </is>
+      </c>
+      <c r="J151" s="6"/>
+      <c r="K151" s="6"/>
+      <c r="L151" s="13"/>
+      <c r="M151" s="13"/>
+      <c r="N151" s="13" t="n">
+        <v>230000.0</v>
+      </c>
+      <c r="O151" s="13" t="n">
+        <v>4670000.0</v>
+      </c>
+      <c r="P151" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q151" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>146.0</v>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H152" s="7"/>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Khánh Ngọc</t>
+        </is>
+      </c>
+      <c r="J152" s="6"/>
+      <c r="K152" s="6"/>
+      <c r="L152" s="13"/>
+      <c r="M152" s="13"/>
+      <c r="N152" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O152" s="13" t="n">
+        <v>1980000.0</v>
+      </c>
+      <c r="P152" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q152" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="n">
+        <v>147.0</v>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H153" s="7"/>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>Trương Vũ Thuận</t>
+        </is>
+      </c>
+      <c r="J153" s="6"/>
+      <c r="K153" s="6"/>
+      <c r="L153" s="13"/>
+      <c r="M153" s="13"/>
+      <c r="N153" s="13" t="n">
+        <v>230000.0</v>
+      </c>
+      <c r="O153" s="13" t="n">
+        <v>4670000.0</v>
+      </c>
+      <c r="P153" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q153" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="n">
+        <v>148.0</v>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>3252</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H154" s="7"/>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Hoàng Minh Hiếu</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="inlineStr">
+        <is>
+          <t>267 Nguyễn An Ninh, Dĩ An Bình Dương (cũ)</t>
+        </is>
+      </c>
+      <c r="K154" s="6"/>
+      <c r="L154" s="13"/>
+      <c r="M154" s="13"/>
+      <c r="N154" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="O154" s="13" t="n">
+        <v>1.157E7</v>
+      </c>
+      <c r="P154" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q154" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="n">
+        <v>149.0</v>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>3253</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H155" s="7"/>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>Lê Nguyễn Đan Thanh</t>
+        </is>
+      </c>
+      <c r="J155" s="6" t="inlineStr">
+        <is>
+          <t>77 Lý Tự Trọng, P. Vũng Tàu, TP.HCM</t>
+        </is>
+      </c>
+      <c r="K155" s="6"/>
+      <c r="L155" s="13"/>
+      <c r="M155" s="13"/>
+      <c r="N155" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O155" s="13" t="n">
+        <v>4725000.0</v>
+      </c>
+      <c r="P155" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q155" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>3254</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H156" s="7"/>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>Lê Nguyễn Đan Thanh</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="inlineStr">
+        <is>
+          <t>77 Lý Tự Trọng, P. Vũng Tàu, TP.HCM</t>
+        </is>
+      </c>
+      <c r="K156" s="6"/>
+      <c r="L156" s="13"/>
+      <c r="M156" s="13"/>
+      <c r="N156" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O156" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P156" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q156" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="n">
+        <v>151.0</v>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H157" s="7"/>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>Sách tiếng anh photto</t>
+        </is>
+      </c>
+      <c r="J157" s="6"/>
+      <c r="K157" s="6"/>
+      <c r="L157" s="13"/>
+      <c r="M157" s="13"/>
+      <c r="N157" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O157" s="13" t="n">
+        <v>4990000.0</v>
+      </c>
+      <c r="P157" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q157" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="n">
+        <v>152.0</v>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>3256</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H158" s="7"/>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>Trần Nhật Khánh An</t>
+        </is>
+      </c>
+      <c r="J158" s="6"/>
+      <c r="K158" s="6"/>
+      <c r="L158" s="13"/>
+      <c r="M158" s="13"/>
+      <c r="N158" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O158" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P158" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q158" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="n">
+        <v>153.0</v>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>3257</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H159" s="7"/>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Chấn Phong</t>
+        </is>
+      </c>
+      <c r="J159" s="6"/>
+      <c r="K159" s="6"/>
+      <c r="L159" s="13"/>
+      <c r="M159" s="13"/>
+      <c r="N159" s="13" t="n">
+        <v>230000.0</v>
+      </c>
+      <c r="O159" s="13" t="n">
+        <v>4670000.0</v>
+      </c>
+      <c r="P159" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q159" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="n">
+        <v>154.0</v>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>3258</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H160" s="7"/>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>Ngô Phạm Hoàng Nam</t>
+        </is>
+      </c>
+      <c r="J160" s="6" t="inlineStr">
+        <is>
+          <t>434/9/20 Phạm Văn Chiêu p9 Gò Vấp TPHCM</t>
+        </is>
+      </c>
+      <c r="K160" s="6"/>
+      <c r="L160" s="13"/>
+      <c r="M160" s="13"/>
+      <c r="N160" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O160" s="13" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="P160" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q160" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="n">
+        <v>155.0</v>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>3259</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H161" s="7"/>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Tuấn Phong</t>
+        </is>
+      </c>
+      <c r="J161" s="6"/>
+      <c r="K161" s="6"/>
+      <c r="L161" s="13"/>
+      <c r="M161" s="13"/>
+      <c r="N161" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O161" s="13" t="n">
+        <v>384000.0</v>
+      </c>
+      <c r="P161" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q161" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="n">
+        <v>156.0</v>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H162" s="7"/>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>Đào Quốc Khang</t>
+        </is>
+      </c>
+      <c r="J162" s="6"/>
+      <c r="K162" s="6"/>
+      <c r="L162" s="13"/>
+      <c r="M162" s="13"/>
+      <c r="N162" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O162" s="13" t="n">
+        <v>6400000.0</v>
+      </c>
+      <c r="P162" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q162" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="n">
+        <v>157.0</v>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>3261</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H163" s="7"/>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>Trần Hoàng Minh An</t>
+        </is>
+      </c>
+      <c r="J163" s="6" t="inlineStr">
+        <is>
+          <t>874A1 đường 30/4 phường Phước Thắng, TP. HCM</t>
+        </is>
+      </c>
+      <c r="K163" s="6"/>
+      <c r="L163" s="13"/>
+      <c r="M163" s="13"/>
+      <c r="N163" s="13" t="n">
+        <v>950000.0</v>
+      </c>
+      <c r="O163" s="13" t="n">
+        <v>3010000.0</v>
+      </c>
+      <c r="P163" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q163" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="n">
+        <v>158.0</v>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>3262</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H164" s="7"/>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>Trần Ngọc Kim Ngân</t>
+        </is>
+      </c>
+      <c r="J164" s="6" t="inlineStr">
+        <is>
+          <t>64 Ấp Thi Tứ, Xã Phong Điền, Cần Thơ</t>
+        </is>
+      </c>
+      <c r="K164" s="6"/>
+      <c r="L164" s="13"/>
+      <c r="M164" s="13"/>
+      <c r="N164" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="O164" s="13" t="n">
+        <v>3780000.0</v>
+      </c>
+      <c r="P164" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q164" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="n">
+        <v>159.0</v>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>3263</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H165" s="7"/>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Như Trà</t>
+        </is>
+      </c>
+      <c r="J165" s="6"/>
+      <c r="K165" s="6"/>
+      <c r="L165" s="13"/>
+      <c r="M165" s="13"/>
+      <c r="N165" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="O165" s="13" t="n">
+        <v>1.138E7</v>
+      </c>
+      <c r="P165" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q165" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="n">
+        <v>160.0</v>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H166" s="7"/>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Như Trà</t>
+        </is>
+      </c>
+      <c r="J166" s="6"/>
+      <c r="K166" s="6"/>
+      <c r="L166" s="13"/>
+      <c r="M166" s="13"/>
+      <c r="N166" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O166" s="13" t="n">
+        <v>243000.0</v>
+      </c>
+      <c r="P166" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q166" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="n">
+        <v>161.0</v>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H167" s="7"/>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Thuỷ Tiên</t>
+        </is>
+      </c>
+      <c r="J167" s="6"/>
+      <c r="K167" s="6"/>
+      <c r="L167" s="13"/>
+      <c r="M167" s="13"/>
+      <c r="N167" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="O167" s="13" t="n">
+        <v>3860000.0</v>
+      </c>
+      <c r="P167" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q167" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="n">
+        <v>162.0</v>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>3266</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H168" s="7"/>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Thuỷ Tiên</t>
+        </is>
+      </c>
+      <c r="J168" s="6"/>
+      <c r="K168" s="6"/>
+      <c r="L168" s="13"/>
+      <c r="M168" s="13"/>
+      <c r="N168" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O168" s="13" t="n">
+        <v>243000.0</v>
+      </c>
+      <c r="P168" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q168" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="n">
+        <v>163.0</v>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H169" s="7"/>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Đức Cao</t>
+        </is>
+      </c>
+      <c r="J169" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14/1, Hàn Thuyên. P. Rạch Dừa, TP. HCM </t>
+        </is>
+      </c>
+      <c r="K169" s="6"/>
+      <c r="L169" s="13"/>
+      <c r="M169" s="13"/>
+      <c r="N169" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="O169" s="13" t="n">
+        <v>8950000.0</v>
+      </c>
+      <c r="P169" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q169" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="n">
+        <v>164.0</v>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H170" s="7"/>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>Lương Quỳnh Nhật Uyển</t>
+        </is>
+      </c>
+      <c r="J170" s="6" t="inlineStr">
+        <is>
+          <t>12, đường Nguyễn Thị Minh Khai, kp4, phường Tân Ninh, tỉnh Tây Ninh</t>
+        </is>
+      </c>
+      <c r="K170" s="6"/>
+      <c r="L170" s="13"/>
+      <c r="M170" s="13"/>
+      <c r="N170" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O170" s="13" t="n">
+        <v>1680000.0</v>
+      </c>
+      <c r="P170" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q170" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="n">
+        <v>165.0</v>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H171" s="7"/>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Đức Mạnh</t>
+        </is>
+      </c>
+      <c r="J171" s="6" t="inlineStr">
+        <is>
+          <t>Xã Phú Thiện, tỉnh Gia Lai</t>
+        </is>
+      </c>
+      <c r="K171" s="6"/>
+      <c r="L171" s="13"/>
+      <c r="M171" s="13"/>
+      <c r="N171" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="O171" s="13" t="n">
+        <v>3780000.0</v>
+      </c>
+      <c r="P171" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q171" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="n">
+        <v>166.0</v>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>3270</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H172" s="7"/>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>Võ Lê Mai Trâm</t>
+        </is>
+      </c>
+      <c r="J172" s="6"/>
+      <c r="K172" s="6"/>
+      <c r="L172" s="13"/>
+      <c r="M172" s="13"/>
+      <c r="N172" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O172" s="13" t="n">
+        <v>3980000.0</v>
+      </c>
+      <c r="P172" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q172" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="n">
+        <v>167.0</v>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>3271</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H173" s="7"/>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>Võ Lê Mai Trâm</t>
+        </is>
+      </c>
+      <c r="J173" s="6"/>
+      <c r="K173" s="6"/>
+      <c r="L173" s="13"/>
+      <c r="M173" s="13"/>
+      <c r="N173" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O173" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P173" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q173" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="n">
+        <v>168.0</v>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>C25MAA</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H174" s="7"/>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>Vũ Minh Phương</t>
+        </is>
+      </c>
+      <c r="J174" s="6" t="inlineStr">
+        <is>
+          <t>Số 52 Lục đầu giang- Tổ dân phố 11- Chí Linh- Hải Phòng</t>
+        </is>
+      </c>
+      <c r="K174" s="6"/>
+      <c r="L174" s="13"/>
+      <c r="M174" s="13"/>
+      <c r="N174" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="O174" s="13" t="n">
+        <v>3780000.0</v>
+      </c>
+      <c r="P174" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q174" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>
